--- a/docs/sales-reform-toolkit/01_棚卸し・スコアリングマスター.xlsx
+++ b/docs/sales-reform-toolkit/01_棚卸し・スコアリングマスター.xlsx
@@ -9,18 +9,19 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ設定" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_顧客棚卸し・ランク" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_案件棚卸し・スコアリング" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_パートナー棚卸し" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_トップ外交管理" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_休眠顧客・再活性化" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="採点定義（顧客ランク）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_顧客棚卸し・ランク" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_案件棚卸し・スコアリング" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_パートナー棚卸し" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_トップ外交管理" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_休眠顧客・再活性化" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'01_顧客棚卸し・ランク'!$A$1:$U$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'02_案件棚卸し・スコアリング'!$A$1:$AC$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'03_パートナー棚卸し'!$A$1:$K$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'04_トップ外交管理'!$A$1:$Q$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'05_休眠顧客・再活性化'!$A$1:$M$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'01_顧客棚卸し・ランク'!$A$1:$U$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02_案件棚卸し・スコアリング'!$A$1:$AC$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03_パートナー棚卸し'!$A$1:$K$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'04_トップ外交管理'!$A$1:$Q$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'05_休眠顧客・再活性化'!$A$1:$M$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +71,24 @@
       <color rgb="003A106E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="005F5F6E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="003A106E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="0026262E"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +103,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EFFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -138,6 +160,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -230,6 +261,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>STO</author>
+  </authors>
+  <commentList>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>①取引実績（データで自動判定）
+5:3年連続かつ上位10% / 4:複数年かつ上位25% / 3:直近1年取引あり中位 / 2:小規模・単発 / 1:実績なし・僅少
+※詳細は「採点定義（顧客ランク）」シート参照。迷ったら低い方の点。</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>②成長性（判断項目）
+5:拡大計画の相談が既にある / 4:拡大意向が商談で出ている / 3:安定・現状維持 / 2:縮小傾向 / 1:撤退リスク・終了兆候
+※詳細は「採点定義（顧客ランク）」シート参照。迷ったら低い方の点。</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>③IP適合（判断項目）
+5:ブランドを高める共創実績 / 4:品質安定・差し戻しほぼ無 / 3:標準 / 2:監修負荷高い / 1:毀損リスク→即エスカレーション
+※詳細は「採点定義（顧客ランク）」シート参照。迷ったら低い方の点。</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>④CRM/D2C価値（判断項目）
+5:会員・データ・送客の仕組み有 / 4:大きなファン接点＋連携余地 / 3:接点あるがデータ不可 / 2:間接的 / 1:寄与なし
+※詳細は「採点定義（顧客ランク）」シート参照。迷ったら低い方の点。</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>⑤海外価値（判断項目）
+5:複数市場で海外売上に直接貢献 / 4:重要市場で強いチャネル / 3:可能性あり未着手 / 2:国内中心 / 1:寄与なし
+※詳細は「採点定義（顧客ランク）」シート参照。迷ったら低い方の点。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1257,6 +1333,322 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>顧客ランク 採点定義（確定版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>共通ルール：①取引実績はデータで自動判定、②〜⑤は判断項目（採点時に根拠を一言メモ）／迷ったら低い方の点／初回はSTO下書き→担当マネージャー確定／見直しは年1回（例外変更は四半期）／合計点でランク自動判定：S≧21・A≧17・B≧12・C＜12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>評価軸</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>測るもの</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>判断材料</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>5点</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>4点</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>3点</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>2点</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>1点</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>留意事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>① 取引実績</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>直近3年の取引の厚み（取引額・粗利・継続性）</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>請求・契約データで自動判定（人の判断を入れない）</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>直近3年連続で取引があり、年間取引額が全顧客の上位10%</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>直近3年のうち複数年取引があり、上位25%</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>直近1年に取引あり、金額は中位</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>直近3年内に取引はあるが、小規模または単発</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>取引実績なし、またはごく僅少（新規・休眠）</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>上位10%/25%の基準は棚卸し完了後に絶対額（年間◯◯円以上）へ置き換えて確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>② 成長性</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>相手企業の事業の勢い × 取引を広げる意思</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>商談記録・相手のIR/業界動向・担当ヒアリング</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>相手の事業が成長中で、具体的な拡大計画・新カテゴリの相談が既にある</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>事業が成長中で、拡大の意向が商談で出ている</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>事業は安定。取引は現状維持の見込み</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>相手の業界・事業が縮小傾向で、取引も漸減</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>事業縮小・撤退リスクがあり、取引終了の兆候</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>「当社を好きか」ではなく「事業として伸びるか×広げる気があるか」で見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>③ IP適合</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>ブランドを高める相手か、毀損リスクはないか</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>監修記録（差し戻し回数）・過去協業の品質・業種と商材</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>ブランド価値を高める協業ができる（世界観理解が深く、品質がブランドを強化した共創実績あり）</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>世界観理解があり、品質基準を安定して満たす（差し戻しほぼなし）</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>標準的。ガイドライン順守に問題なし</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>品質・表現面で監修負荷が高い（差し戻し頻発）</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>毀損リスクあり（業種・表現・品質・価格帯がブランドと不整合）</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>1点がついた顧客は合計点に関わらずエスカレーション（取引可否を経営判断）。毀損条件の明文化はブランド基準WGと連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>④ CRM/D2C価値</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>ファンとの直接のつながりをどれだけ生むか</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>案件スキーム・相手の会員基盤とチャネル</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>会員獲得・データ取得・D2C送客の仕組みが取引に組み込まれている（またはすぐ組める）</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>来店・体験・キャンペーン等の大きなファン接点があり、データ連携の余地あり</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>エンドユーザーとの接点はあるが、データは取れない</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>ファンとの接点が間接的・限定的</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>ファン接点にほぼ寄与しない</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>⑤ 海外価値</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>海外展開の扉をどれだけ開けるか</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>相手の海外拠点・販路・過去の海外展開実績</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>複数市場で展開力があり、海外売上に直接貢献（または重要市場攻略の鍵）</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>特定の重要市場で強いチャネル・実績を持つ</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>海外展開の可能性はあるが未着手</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>国内中心で、海外への波及は限定的</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>海外展開に寄与しない</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7836,10 +8228,11 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18473,7 +18866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21201,7 +21594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26359,7 +26752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
